--- a/Excel/FashionConfig.xlsx
+++ b/Excel/FashionConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -119,7 +119,7 @@
     <t>int[]</t>
   </si>
   <si>
-    <t>战神之刃</t>
+    <t>斩仙之刃</t>
   </si>
   <si>
     <t>14,16,15,26</t>
@@ -128,154 +128,154 @@
     <t>5,5,5,5</t>
   </si>
   <si>
-    <t>战神之甲</t>
-  </si>
-  <si>
-    <t>战神之头</t>
-  </si>
-  <si>
-    <t>战神之链</t>
-  </si>
-  <si>
-    <t>战神之镯</t>
-  </si>
-  <si>
-    <t>战神之戒</t>
-  </si>
-  <si>
-    <t>战神之带</t>
-  </si>
-  <si>
-    <t>战神之靴</t>
-  </si>
-  <si>
-    <t>恶魔之杖</t>
+    <t>斩仙之甲</t>
+  </si>
+  <si>
+    <t>斩仙之头</t>
+  </si>
+  <si>
+    <t>斩仙之链</t>
+  </si>
+  <si>
+    <t>斩仙之镯</t>
+  </si>
+  <si>
+    <t>斩仙之戒</t>
+  </si>
+  <si>
+    <t>斩仙之带</t>
+  </si>
+  <si>
+    <t>斩仙之靴</t>
+  </si>
+  <si>
+    <t>魔尊之杖</t>
   </si>
   <si>
     <t>14,16,15,27</t>
   </si>
   <si>
-    <t>恶魔之衣</t>
-  </si>
-  <si>
-    <t>恶魔之头</t>
-  </si>
-  <si>
-    <t>恶魔之链</t>
-  </si>
-  <si>
-    <t>恶魔之镯</t>
-  </si>
-  <si>
-    <t>恶魔之戒</t>
-  </si>
-  <si>
-    <t>恶魔之带</t>
-  </si>
-  <si>
-    <t>恶魔之靴</t>
-  </si>
-  <si>
-    <t>幽灵之剑</t>
+    <t>魔尊之衣</t>
+  </si>
+  <si>
+    <t>魔尊之头</t>
+  </si>
+  <si>
+    <t>魔尊之链</t>
+  </si>
+  <si>
+    <t>魔尊之镯</t>
+  </si>
+  <si>
+    <t>魔尊之戒</t>
+  </si>
+  <si>
+    <t>魔尊之带</t>
+  </si>
+  <si>
+    <t>魔尊之靴</t>
+  </si>
+  <si>
+    <t>幽冥之剑</t>
   </si>
   <si>
     <t>14,16,15,28</t>
   </si>
   <si>
-    <t>幽灵之袍</t>
-  </si>
-  <si>
-    <t>幽灵之头</t>
-  </si>
-  <si>
-    <t>幽灵之链</t>
-  </si>
-  <si>
-    <t>幽灵之镯</t>
-  </si>
-  <si>
-    <t>幽灵之戒</t>
-  </si>
-  <si>
-    <t>幽灵之带</t>
-  </si>
-  <si>
-    <t>幽灵之靴</t>
-  </si>
-  <si>
-    <t>圣战之刃</t>
+    <t>幽冥之袍</t>
+  </si>
+  <si>
+    <t>幽冥之头</t>
+  </si>
+  <si>
+    <t>幽冥之链</t>
+  </si>
+  <si>
+    <t>幽冥之镯</t>
+  </si>
+  <si>
+    <t>幽冥之戒</t>
+  </si>
+  <si>
+    <t>幽冥之带</t>
+  </si>
+  <si>
+    <t>幽冥之靴</t>
+  </si>
+  <si>
+    <t>战魂之刃</t>
   </si>
   <si>
     <t>10,10,10,10</t>
   </si>
   <si>
-    <t>圣战之甲</t>
-  </si>
-  <si>
-    <t>圣战之头</t>
-  </si>
-  <si>
-    <t>圣战之链</t>
-  </si>
-  <si>
-    <t>圣战之镯</t>
-  </si>
-  <si>
-    <t>圣战之戒</t>
-  </si>
-  <si>
-    <t>圣战之带</t>
-  </si>
-  <si>
-    <t>圣战之靴</t>
-  </si>
-  <si>
-    <t>法神之杖</t>
-  </si>
-  <si>
-    <t>法神之衣</t>
-  </si>
-  <si>
-    <t>法神之头</t>
-  </si>
-  <si>
-    <t>法神之链</t>
-  </si>
-  <si>
-    <t>法神之镯</t>
-  </si>
-  <si>
-    <t>法神之戒</t>
-  </si>
-  <si>
-    <t>法神之带</t>
-  </si>
-  <si>
-    <t>法神之靴</t>
-  </si>
-  <si>
-    <t>天尊之剑</t>
-  </si>
-  <si>
-    <t>天尊之袍</t>
-  </si>
-  <si>
-    <t>天尊之头</t>
-  </si>
-  <si>
-    <t>天尊之链</t>
-  </si>
-  <si>
-    <t>天尊之镯</t>
-  </si>
-  <si>
-    <t>天尊之戒</t>
-  </si>
-  <si>
-    <t>天尊之带</t>
-  </si>
-  <si>
-    <t>天尊之靴</t>
+    <t>战魂之甲</t>
+  </si>
+  <si>
+    <t>战魂之头</t>
+  </si>
+  <si>
+    <t>战魂之链</t>
+  </si>
+  <si>
+    <t>战魂之镯</t>
+  </si>
+  <si>
+    <t>战魂之戒</t>
+  </si>
+  <si>
+    <t>战魂之带</t>
+  </si>
+  <si>
+    <t>战魂之靴</t>
+  </si>
+  <si>
+    <t>法魂之杖</t>
+  </si>
+  <si>
+    <t>法魂之衣</t>
+  </si>
+  <si>
+    <t>法魂之头</t>
+  </si>
+  <si>
+    <t>法魂之链</t>
+  </si>
+  <si>
+    <t>法魂之镯</t>
+  </si>
+  <si>
+    <t>法魂之戒</t>
+  </si>
+  <si>
+    <t>法魂之带</t>
+  </si>
+  <si>
+    <t>法魂之靴</t>
+  </si>
+  <si>
+    <t>道魂之剑</t>
+  </si>
+  <si>
+    <t>道魂之袍</t>
+  </si>
+  <si>
+    <t>道魂之头</t>
+  </si>
+  <si>
+    <t>道魂之链</t>
+  </si>
+  <si>
+    <t>道魂之镯</t>
+  </si>
+  <si>
+    <t>道魂之戒</t>
+  </si>
+  <si>
+    <t>道魂之带</t>
+  </si>
+  <si>
+    <t>道魂之靴</t>
   </si>
 </sst>
 </file>
@@ -461,12 +461,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -926,7 +926,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -934,6 +934,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1383,13 +1384,13 @@
       <c r="G6" s="1">
         <v>1</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="H6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="I6" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="J6" s="5" t="s">
+      <c r="I6" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J6" s="6" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1409,13 +1410,13 @@
       <c r="G7" s="1">
         <v>1</v>
       </c>
-      <c r="H7" s="5" t="s">
+      <c r="H7" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="I7" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="J7" s="5" t="s">
+      <c r="I7" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J7" s="6" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1435,13 +1436,13 @@
       <c r="G8" s="1">
         <v>1</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="H8" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="I8" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="J8" s="5" t="s">
+      <c r="I8" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J8" s="6" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1461,13 +1462,13 @@
       <c r="G9" s="1">
         <v>1</v>
       </c>
-      <c r="H9" s="5" t="s">
+      <c r="H9" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="I9" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="J9" s="5" t="s">
+      <c r="I9" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J9" s="6" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1487,13 +1488,13 @@
       <c r="G10" s="1">
         <v>1</v>
       </c>
-      <c r="H10" s="5" t="s">
+      <c r="H10" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="I10" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="J10" s="5" t="s">
+      <c r="I10" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J10" s="6" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1513,13 +1514,13 @@
       <c r="G11" s="1">
         <v>1</v>
       </c>
-      <c r="H11" s="5" t="s">
+      <c r="H11" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="I11" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="J11" s="5" t="s">
+      <c r="I11" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J11" s="6" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1539,13 +1540,13 @@
       <c r="G12" s="1">
         <v>1</v>
       </c>
-      <c r="H12" s="5" t="s">
+      <c r="H12" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="I12" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="J12" s="5" t="s">
+      <c r="I12" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J12" s="6" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1565,13 +1566,13 @@
       <c r="G13" s="1">
         <v>1</v>
       </c>
-      <c r="H13" s="5" t="s">
+      <c r="H13" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="I13" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="J13" s="5" t="s">
+      <c r="I13" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J13" s="6" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1591,13 +1592,13 @@
       <c r="G14" s="1">
         <v>2</v>
       </c>
-      <c r="H14" s="5" t="s">
+      <c r="H14" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="I14" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="J14" s="5" t="s">
+      <c r="I14" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J14" s="6" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1617,13 +1618,13 @@
       <c r="G15" s="1">
         <v>2</v>
       </c>
-      <c r="H15" s="5" t="s">
+      <c r="H15" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="I15" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="J15" s="5" t="s">
+      <c r="I15" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J15" s="6" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1643,13 +1644,13 @@
       <c r="G16" s="1">
         <v>2</v>
       </c>
-      <c r="H16" s="5" t="s">
+      <c r="H16" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="I16" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="J16" s="5" t="s">
+      <c r="I16" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J16" s="6" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1669,13 +1670,13 @@
       <c r="G17" s="1">
         <v>2</v>
       </c>
-      <c r="H17" s="5" t="s">
+      <c r="H17" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="I17" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="J17" s="5" t="s">
+      <c r="I17" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J17" s="6" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1695,13 +1696,13 @@
       <c r="G18" s="1">
         <v>2</v>
       </c>
-      <c r="H18" s="5" t="s">
+      <c r="H18" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="I18" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="J18" s="5" t="s">
+      <c r="I18" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J18" s="6" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1721,13 +1722,13 @@
       <c r="G19" s="1">
         <v>2</v>
       </c>
-      <c r="H19" s="5" t="s">
+      <c r="H19" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="I19" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="J19" s="5" t="s">
+      <c r="I19" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J19" s="6" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1747,13 +1748,13 @@
       <c r="G20" s="1">
         <v>2</v>
       </c>
-      <c r="H20" s="5" t="s">
+      <c r="H20" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="I20" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="J20" s="5" t="s">
+      <c r="I20" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J20" s="6" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1773,13 +1774,13 @@
       <c r="G21" s="1">
         <v>2</v>
       </c>
-      <c r="H21" s="5" t="s">
+      <c r="H21" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="I21" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="J21" s="5" t="s">
+      <c r="I21" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J21" s="6" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1790,7 +1791,7 @@
       <c r="D22" s="4">
         <v>3000017</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="E22" s="5" t="s">
         <v>31</v>
       </c>
       <c r="F22" s="1">
@@ -1799,13 +1800,13 @@
       <c r="G22" s="1">
         <v>3</v>
       </c>
-      <c r="H22" s="5" t="s">
+      <c r="H22" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="I22" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="J22" s="5" t="s">
+      <c r="I22" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J22" s="6" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1816,7 +1817,7 @@
       <c r="D23" s="4">
         <v>3000018</v>
       </c>
-      <c r="E23" s="1" t="s">
+      <c r="E23" s="5" t="s">
         <v>33</v>
       </c>
       <c r="F23" s="1">
@@ -1825,13 +1826,13 @@
       <c r="G23" s="1">
         <v>3</v>
       </c>
-      <c r="H23" s="5" t="s">
+      <c r="H23" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="I23" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="J23" s="5" t="s">
+      <c r="I23" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J23" s="6" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1842,7 +1843,7 @@
       <c r="D24" s="4">
         <v>3000019</v>
       </c>
-      <c r="E24" s="1" t="s">
+      <c r="E24" s="5" t="s">
         <v>34</v>
       </c>
       <c r="F24" s="1">
@@ -1851,13 +1852,13 @@
       <c r="G24" s="1">
         <v>3</v>
       </c>
-      <c r="H24" s="5" t="s">
+      <c r="H24" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="I24" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="J24" s="5" t="s">
+      <c r="I24" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J24" s="6" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1868,7 +1869,7 @@
       <c r="D25" s="4">
         <v>3000020</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="E25" s="5" t="s">
         <v>35</v>
       </c>
       <c r="F25" s="1">
@@ -1877,13 +1878,13 @@
       <c r="G25" s="1">
         <v>3</v>
       </c>
-      <c r="H25" s="5" t="s">
+      <c r="H25" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="I25" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="J25" s="5" t="s">
+      <c r="I25" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J25" s="6" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1894,7 +1895,7 @@
       <c r="D26" s="4">
         <v>3000021</v>
       </c>
-      <c r="E26" s="1" t="s">
+      <c r="E26" s="5" t="s">
         <v>36</v>
       </c>
       <c r="F26" s="1">
@@ -1903,13 +1904,13 @@
       <c r="G26" s="1">
         <v>3</v>
       </c>
-      <c r="H26" s="5" t="s">
+      <c r="H26" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="I26" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="J26" s="5" t="s">
+      <c r="I26" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J26" s="6" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1920,7 +1921,7 @@
       <c r="D27" s="4">
         <v>3000022</v>
       </c>
-      <c r="E27" s="1" t="s">
+      <c r="E27" s="5" t="s">
         <v>37</v>
       </c>
       <c r="F27" s="1">
@@ -1929,13 +1930,13 @@
       <c r="G27" s="1">
         <v>3</v>
       </c>
-      <c r="H27" s="5" t="s">
+      <c r="H27" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="I27" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="J27" s="5" t="s">
+      <c r="I27" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J27" s="6" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1946,7 +1947,7 @@
       <c r="D28" s="4">
         <v>3000023</v>
       </c>
-      <c r="E28" s="1" t="s">
+      <c r="E28" s="5" t="s">
         <v>38</v>
       </c>
       <c r="F28" s="1">
@@ -1955,13 +1956,13 @@
       <c r="G28" s="1">
         <v>3</v>
       </c>
-      <c r="H28" s="5" t="s">
+      <c r="H28" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="I28" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="J28" s="5" t="s">
+      <c r="I28" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J28" s="6" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1972,7 +1973,7 @@
       <c r="D29" s="4">
         <v>3000024</v>
       </c>
-      <c r="E29" s="1" t="s">
+      <c r="E29" s="5" t="s">
         <v>39</v>
       </c>
       <c r="F29" s="1">
@@ -1981,13 +1982,13 @@
       <c r="G29" s="1">
         <v>3</v>
       </c>
-      <c r="H29" s="5" t="s">
+      <c r="H29" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="I29" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="J29" s="5" t="s">
+      <c r="I29" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J29" s="6" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2007,13 +2008,13 @@
       <c r="G30" s="1">
         <v>4</v>
       </c>
-      <c r="H30" s="5" t="s">
+      <c r="H30" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="I30" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="J30" s="5" t="s">
+      <c r="I30" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="J30" s="6" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2033,13 +2034,13 @@
       <c r="G31" s="1">
         <v>4</v>
       </c>
-      <c r="H31" s="5" t="s">
+      <c r="H31" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="I31" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="J31" s="5" t="s">
+      <c r="I31" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="J31" s="6" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2059,13 +2060,13 @@
       <c r="G32" s="1">
         <v>4</v>
       </c>
-      <c r="H32" s="5" t="s">
+      <c r="H32" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="I32" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="J32" s="5" t="s">
+      <c r="I32" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="J32" s="6" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2085,13 +2086,13 @@
       <c r="G33" s="1">
         <v>4</v>
       </c>
-      <c r="H33" s="5" t="s">
+      <c r="H33" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="I33" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="J33" s="5" t="s">
+      <c r="I33" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="J33" s="6" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2111,13 +2112,13 @@
       <c r="G34" s="1">
         <v>4</v>
       </c>
-      <c r="H34" s="5" t="s">
+      <c r="H34" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="I34" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="J34" s="5" t="s">
+      <c r="I34" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="J34" s="6" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2137,13 +2138,13 @@
       <c r="G35" s="1">
         <v>4</v>
       </c>
-      <c r="H35" s="5" t="s">
+      <c r="H35" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="I35" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="J35" s="5" t="s">
+      <c r="I35" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="J35" s="6" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2163,13 +2164,13 @@
       <c r="G36" s="1">
         <v>4</v>
       </c>
-      <c r="H36" s="5" t="s">
+      <c r="H36" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="I36" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="J36" s="5" t="s">
+      <c r="I36" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="J36" s="6" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2189,13 +2190,13 @@
       <c r="G37" s="1">
         <v>4</v>
       </c>
-      <c r="H37" s="5" t="s">
+      <c r="H37" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="I37" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="J37" s="5" t="s">
+      <c r="I37" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="J37" s="6" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2215,13 +2216,13 @@
       <c r="G38" s="1">
         <v>5</v>
       </c>
-      <c r="H38" s="5" t="s">
+      <c r="H38" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="I38" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="J38" s="5" t="s">
+      <c r="I38" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="J38" s="6" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2241,13 +2242,13 @@
       <c r="G39" s="1">
         <v>5</v>
       </c>
-      <c r="H39" s="5" t="s">
+      <c r="H39" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="I39" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="J39" s="5" t="s">
+      <c r="I39" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="J39" s="6" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2267,13 +2268,13 @@
       <c r="G40" s="1">
         <v>5</v>
       </c>
-      <c r="H40" s="5" t="s">
+      <c r="H40" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="I40" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="J40" s="5" t="s">
+      <c r="I40" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="J40" s="6" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2293,13 +2294,13 @@
       <c r="G41" s="1">
         <v>5</v>
       </c>
-      <c r="H41" s="5" t="s">
+      <c r="H41" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="I41" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="J41" s="5" t="s">
+      <c r="I41" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="J41" s="6" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2319,13 +2320,13 @@
       <c r="G42" s="1">
         <v>5</v>
       </c>
-      <c r="H42" s="5" t="s">
+      <c r="H42" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="I42" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="J42" s="5" t="s">
+      <c r="I42" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="J42" s="6" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2345,13 +2346,13 @@
       <c r="G43" s="1">
         <v>5</v>
       </c>
-      <c r="H43" s="5" t="s">
+      <c r="H43" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="I43" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="J43" s="5" t="s">
+      <c r="I43" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="J43" s="6" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2371,13 +2372,13 @@
       <c r="G44" s="1">
         <v>5</v>
       </c>
-      <c r="H44" s="5" t="s">
+      <c r="H44" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="I44" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="J44" s="5" t="s">
+      <c r="I44" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="J44" s="6" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2397,13 +2398,13 @@
       <c r="G45" s="1">
         <v>5</v>
       </c>
-      <c r="H45" s="5" t="s">
+      <c r="H45" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="I45" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="J45" s="5" t="s">
+      <c r="I45" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="J45" s="6" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2423,13 +2424,13 @@
       <c r="G46" s="1">
         <v>6</v>
       </c>
-      <c r="H46" s="5" t="s">
+      <c r="H46" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="I46" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="J46" s="5" t="s">
+      <c r="I46" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="J46" s="6" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2449,13 +2450,13 @@
       <c r="G47" s="1">
         <v>6</v>
       </c>
-      <c r="H47" s="5" t="s">
+      <c r="H47" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="I47" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="J47" s="5" t="s">
+      <c r="I47" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="J47" s="6" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2475,13 +2476,13 @@
       <c r="G48" s="1">
         <v>6</v>
       </c>
-      <c r="H48" s="5" t="s">
+      <c r="H48" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="I48" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="J48" s="5" t="s">
+      <c r="I48" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="J48" s="6" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2501,13 +2502,13 @@
       <c r="G49" s="1">
         <v>6</v>
       </c>
-      <c r="H49" s="5" t="s">
+      <c r="H49" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="I49" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="J49" s="5" t="s">
+      <c r="I49" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="J49" s="6" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2527,13 +2528,13 @@
       <c r="G50" s="1">
         <v>6</v>
       </c>
-      <c r="H50" s="5" t="s">
+      <c r="H50" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="I50" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="J50" s="5" t="s">
+      <c r="I50" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="J50" s="6" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2553,13 +2554,13 @@
       <c r="G51" s="1">
         <v>6</v>
       </c>
-      <c r="H51" s="5" t="s">
+      <c r="H51" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="I51" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="J51" s="5" t="s">
+      <c r="I51" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="J51" s="6" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2579,13 +2580,13 @@
       <c r="G52" s="1">
         <v>6</v>
       </c>
-      <c r="H52" s="5" t="s">
+      <c r="H52" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="I52" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="J52" s="5" t="s">
+      <c r="I52" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="J52" s="6" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2605,19 +2606,19 @@
       <c r="G53" s="1">
         <v>6</v>
       </c>
-      <c r="H53" s="5" t="s">
+      <c r="H53" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="I53" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="J53" s="5" t="s">
+      <c r="I53" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="J53" s="6" t="s">
         <v>41</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="D3 E3 F3 G3 H3 I3 J3 D4 E4 F4 G4 H4 I4 J4 D5 E5 F5 G5 H5 I5 J5 C3:C5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="D3:J3 E4:J4 E5:J5 C3:C5 D4:D5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/FashionConfig.xlsx
+++ b/Excel/FashionConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27952" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -81,7 +81,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="84">
   <si>
     <t>ID</t>
   </si>
@@ -276,6 +276,63 @@
   </si>
   <si>
     <t>道魂之靴</t>
+  </si>
+  <si>
+    <t>天神之刃</t>
+  </si>
+  <si>
+    <t>7,8,2002,2003</t>
+  </si>
+  <si>
+    <t>1,1,1,1</t>
+  </si>
+  <si>
+    <t>天神之甲</t>
+  </si>
+  <si>
+    <t>天神之头</t>
+  </si>
+  <si>
+    <t>天神之链</t>
+  </si>
+  <si>
+    <t>天神之镯</t>
+  </si>
+  <si>
+    <t>天神之戒</t>
+  </si>
+  <si>
+    <t>天神之带</t>
+  </si>
+  <si>
+    <t>天神之靴</t>
+  </si>
+  <si>
+    <t>魔神之杖</t>
+  </si>
+  <si>
+    <t>12,13,2002,2003</t>
+  </si>
+  <si>
+    <t>魔神之衣</t>
+  </si>
+  <si>
+    <t>魔神之头</t>
+  </si>
+  <si>
+    <t>魔神之链</t>
+  </si>
+  <si>
+    <t>魔神之镯</t>
+  </si>
+  <si>
+    <t>魔神之戒</t>
+  </si>
+  <si>
+    <t>魔神之带</t>
+  </si>
+  <si>
+    <t>魔神之靴</t>
   </si>
 </sst>
 </file>
@@ -461,12 +518,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1255,17 +1312,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J53"/>
+  <dimension ref="A1:J77"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
+    <col min="1" max="1" width="6.87610619469027" style="2" customWidth="1"/>
     <col min="2" max="2" width="9" style="2"/>
-    <col min="3" max="4" width="9.875" style="1" customWidth="1"/>
-    <col min="5" max="6" width="12.125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12.5" style="1" customWidth="1"/>
+    <col min="3" max="4" width="9.87610619469027" style="1" customWidth="1"/>
+    <col min="5" max="6" width="12.1238938053097" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.5044247787611" style="1" customWidth="1"/>
     <col min="8" max="8" width="13" style="2" customWidth="1"/>
-    <col min="9" max="9" width="10.125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="14.875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="10.1238938053097" style="2" customWidth="1"/>
+    <col min="10" max="10" width="14.8761061946903" style="2" customWidth="1"/>
     <col min="11" max="16371" width="9" style="2"/>
     <col min="16372" max="16384" width="9" style="1"/>
   </cols>
@@ -2616,9 +2673,497 @@
         <v>41</v>
       </c>
     </row>
+    <row r="54" customHeight="1" spans="3:10">
+      <c r="C54" s="1">
+        <v>49</v>
+      </c>
+      <c r="D54" s="4">
+        <v>3000049</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F54" s="1">
+        <v>1</v>
+      </c>
+      <c r="G54" s="1">
+        <v>7</v>
+      </c>
+      <c r="H54" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="I54" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J54" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="55" customHeight="1" spans="3:10">
+      <c r="C55" s="1">
+        <v>50</v>
+      </c>
+      <c r="D55" s="4">
+        <v>3000050</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F55" s="1">
+        <v>2</v>
+      </c>
+      <c r="G55" s="1">
+        <v>7</v>
+      </c>
+      <c r="H55" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="I55" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J55" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="56" customHeight="1" spans="3:10">
+      <c r="C56" s="1">
+        <v>51</v>
+      </c>
+      <c r="D56" s="4">
+        <v>3000051</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F56" s="1">
+        <v>3</v>
+      </c>
+      <c r="G56" s="1">
+        <v>7</v>
+      </c>
+      <c r="H56" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="I56" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J56" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="57" customHeight="1" spans="3:10">
+      <c r="C57" s="1">
+        <v>52</v>
+      </c>
+      <c r="D57" s="4">
+        <v>3000052</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F57" s="1">
+        <v>4</v>
+      </c>
+      <c r="G57" s="1">
+        <v>7</v>
+      </c>
+      <c r="H57" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="I57" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J57" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="58" customHeight="1" spans="3:10">
+      <c r="C58" s="1">
+        <v>53</v>
+      </c>
+      <c r="D58" s="4">
+        <v>3000053</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F58" s="1">
+        <v>5</v>
+      </c>
+      <c r="G58" s="1">
+        <v>7</v>
+      </c>
+      <c r="H58" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="I58" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J58" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="59" customHeight="1" spans="3:10">
+      <c r="C59" s="1">
+        <v>54</v>
+      </c>
+      <c r="D59" s="4">
+        <v>3000054</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F59" s="1">
+        <v>6</v>
+      </c>
+      <c r="G59" s="1">
+        <v>7</v>
+      </c>
+      <c r="H59" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="I59" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J59" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="60" customHeight="1" spans="3:10">
+      <c r="C60" s="1">
+        <v>55</v>
+      </c>
+      <c r="D60" s="4">
+        <v>3000055</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F60" s="1">
+        <v>7</v>
+      </c>
+      <c r="G60" s="1">
+        <v>7</v>
+      </c>
+      <c r="H60" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="I60" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J60" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="61" customHeight="1" spans="3:10">
+      <c r="C61" s="1">
+        <v>56</v>
+      </c>
+      <c r="D61" s="4">
+        <v>3000056</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F61" s="1">
+        <v>8</v>
+      </c>
+      <c r="G61" s="1">
+        <v>7</v>
+      </c>
+      <c r="H61" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="I61" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J61" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="62" customHeight="1" spans="3:10">
+      <c r="C62" s="1">
+        <v>57</v>
+      </c>
+      <c r="D62" s="4">
+        <v>3000057</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F62" s="1">
+        <v>1</v>
+      </c>
+      <c r="G62" s="1">
+        <v>8</v>
+      </c>
+      <c r="H62" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="I62" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J62" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="63" customHeight="1" spans="3:10">
+      <c r="C63" s="1">
+        <v>58</v>
+      </c>
+      <c r="D63" s="4">
+        <v>3000058</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F63" s="1">
+        <v>2</v>
+      </c>
+      <c r="G63" s="1">
+        <v>8</v>
+      </c>
+      <c r="H63" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="I63" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J63" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="64" customHeight="1" spans="3:10">
+      <c r="C64" s="1">
+        <v>59</v>
+      </c>
+      <c r="D64" s="4">
+        <v>3000059</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F64" s="1">
+        <v>3</v>
+      </c>
+      <c r="G64" s="1">
+        <v>8</v>
+      </c>
+      <c r="H64" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="I64" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J64" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="65" customHeight="1" spans="3:10">
+      <c r="C65" s="1">
+        <v>60</v>
+      </c>
+      <c r="D65" s="4">
+        <v>3000060</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F65" s="1">
+        <v>4</v>
+      </c>
+      <c r="G65" s="1">
+        <v>8</v>
+      </c>
+      <c r="H65" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="I65" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J65" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="66" customHeight="1" spans="3:10">
+      <c r="C66" s="1">
+        <v>61</v>
+      </c>
+      <c r="D66" s="4">
+        <v>3000061</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F66" s="1">
+        <v>5</v>
+      </c>
+      <c r="G66" s="1">
+        <v>8</v>
+      </c>
+      <c r="H66" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="I66" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J66" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="67" customHeight="1" spans="3:10">
+      <c r="C67" s="1">
+        <v>62</v>
+      </c>
+      <c r="D67" s="4">
+        <v>3000062</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F67" s="1">
+        <v>6</v>
+      </c>
+      <c r="G67" s="1">
+        <v>8</v>
+      </c>
+      <c r="H67" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="I67" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J67" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="68" customHeight="1" spans="3:10">
+      <c r="C68" s="1">
+        <v>63</v>
+      </c>
+      <c r="D68" s="4">
+        <v>3000063</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F68" s="1">
+        <v>7</v>
+      </c>
+      <c r="G68" s="1">
+        <v>8</v>
+      </c>
+      <c r="H68" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="I68" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J68" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="69" customHeight="1" spans="3:10">
+      <c r="C69" s="1">
+        <v>64</v>
+      </c>
+      <c r="D69" s="4">
+        <v>3000064</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F69" s="1">
+        <v>8</v>
+      </c>
+      <c r="G69" s="1">
+        <v>8</v>
+      </c>
+      <c r="H69" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="I69" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J69" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="70" customHeight="1" spans="4:10">
+      <c r="D70" s="4"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="1"/>
+    </row>
+    <row r="71" customHeight="1" spans="4:10">
+      <c r="D71" s="4"/>
+      <c r="E71" s="1"/>
+      <c r="F71" s="1"/>
+      <c r="G71" s="1"/>
+      <c r="H71" s="1"/>
+      <c r="I71" s="1"/>
+      <c r="J71" s="1"/>
+    </row>
+    <row r="72" customHeight="1" spans="4:10">
+      <c r="D72" s="4"/>
+      <c r="E72" s="1"/>
+      <c r="F72" s="1"/>
+      <c r="G72" s="1"/>
+      <c r="H72" s="1"/>
+      <c r="I72" s="1"/>
+      <c r="J72" s="1"/>
+    </row>
+    <row r="73" customHeight="1" spans="4:10">
+      <c r="D73" s="4"/>
+      <c r="E73" s="1"/>
+      <c r="F73" s="1"/>
+      <c r="G73" s="1"/>
+      <c r="H73" s="1"/>
+      <c r="I73" s="1"/>
+      <c r="J73" s="1"/>
+    </row>
+    <row r="74" customHeight="1" spans="4:10">
+      <c r="D74" s="4"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+      <c r="J74" s="1"/>
+    </row>
+    <row r="75" customHeight="1" spans="4:10">
+      <c r="D75" s="4"/>
+      <c r="E75" s="1"/>
+      <c r="F75" s="1"/>
+      <c r="G75" s="1"/>
+      <c r="H75" s="1"/>
+      <c r="I75" s="1"/>
+      <c r="J75" s="1"/>
+    </row>
+    <row r="76" customHeight="1" spans="4:10">
+      <c r="D76" s="4"/>
+      <c r="E76" s="1"/>
+      <c r="F76" s="1"/>
+      <c r="G76" s="1"/>
+      <c r="H76" s="1"/>
+      <c r="I76" s="1"/>
+      <c r="J76" s="1"/>
+    </row>
+    <row r="77" customHeight="1" spans="4:10">
+      <c r="D77" s="4"/>
+      <c r="E77" s="1"/>
+      <c r="F77" s="1"/>
+      <c r="G77" s="1"/>
+      <c r="H77" s="1"/>
+      <c r="I77" s="1"/>
+      <c r="J77" s="1"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="D3:J3 E4:J4 E5:J5 C3:C5 D4:D5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:J5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/FashionConfig.xlsx
+++ b/Excel/FashionConfig.xlsx
@@ -81,7 +81,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="96">
   <si>
     <t>ID</t>
   </si>
@@ -281,7 +281,7 @@
     <t>天神之刃</t>
   </si>
   <si>
-    <t>7,8,2002,2003</t>
+    <t>7,8,33,2001</t>
   </si>
   <si>
     <t>1,1,1,1</t>
@@ -290,46 +290,82 @@
     <t>天神之甲</t>
   </si>
   <si>
+    <t>7,8,34,2002</t>
+  </si>
+  <si>
     <t>天神之头</t>
   </si>
   <si>
+    <t>7,8,35,2002</t>
+  </si>
+  <si>
     <t>天神之链</t>
   </si>
   <si>
+    <t>7,8,9,2003</t>
+  </si>
+  <si>
     <t>天神之镯</t>
   </si>
   <si>
+    <t>7,8,33,2002</t>
+  </si>
+  <si>
     <t>天神之戒</t>
   </si>
   <si>
+    <t>7,8,34,2001</t>
+  </si>
+  <si>
     <t>天神之带</t>
   </si>
   <si>
+    <t>7,8,35,2003</t>
+  </si>
+  <si>
     <t>天神之靴</t>
   </si>
   <si>
     <t>魔神之杖</t>
   </si>
   <si>
-    <t>12,13,2002,2003</t>
+    <t>12,13,33,2001</t>
   </si>
   <si>
     <t>魔神之衣</t>
   </si>
   <si>
+    <t>12,13,34,2002</t>
+  </si>
+  <si>
     <t>魔神之头</t>
   </si>
   <si>
+    <t>12,13,35,2002</t>
+  </si>
+  <si>
     <t>魔神之链</t>
   </si>
   <si>
+    <t>12,13,9,2003</t>
+  </si>
+  <si>
     <t>魔神之镯</t>
   </si>
   <si>
+    <t>12,13,33,2002</t>
+  </si>
+  <si>
     <t>魔神之戒</t>
   </si>
   <si>
+    <t>12,13,34,2001</t>
+  </si>
+  <si>
     <t>魔神之带</t>
+  </si>
+  <si>
+    <t>12,13,35,2003</t>
   </si>
   <si>
     <t>魔神之靴</t>
@@ -1320,7 +1356,7 @@
     <col min="3" max="4" width="9.87610619469027" style="1" customWidth="1"/>
     <col min="5" max="6" width="12.1238938053097" style="1" customWidth="1"/>
     <col min="7" max="7" width="12.5044247787611" style="1" customWidth="1"/>
-    <col min="8" max="8" width="13" style="2" customWidth="1"/>
+    <col min="8" max="8" width="17.7964601769912" style="2" customWidth="1"/>
     <col min="9" max="9" width="10.1238938053097" style="2" customWidth="1"/>
     <col min="10" max="10" width="14.8761061946903" style="2" customWidth="1"/>
     <col min="11" max="16371" width="9" style="2"/>
@@ -2716,7 +2752,7 @@
         <v>7</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="I55" s="6" t="s">
         <v>67</v>
@@ -2733,7 +2769,7 @@
         <v>3000051</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F56" s="1">
         <v>3</v>
@@ -2742,7 +2778,7 @@
         <v>7</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="I56" s="6" t="s">
         <v>67</v>
@@ -2759,7 +2795,7 @@
         <v>3000052</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F57" s="1">
         <v>4</v>
@@ -2768,7 +2804,7 @@
         <v>7</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="I57" s="6" t="s">
         <v>67</v>
@@ -2785,7 +2821,7 @@
         <v>3000053</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F58" s="1">
         <v>5</v>
@@ -2794,7 +2830,7 @@
         <v>7</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="I58" s="6" t="s">
         <v>67</v>
@@ -2811,7 +2847,7 @@
         <v>3000054</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F59" s="1">
         <v>6</v>
@@ -2820,7 +2856,7 @@
         <v>7</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="I59" s="6" t="s">
         <v>67</v>
@@ -2837,7 +2873,7 @@
         <v>3000055</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="F60" s="1">
         <v>7</v>
@@ -2846,7 +2882,7 @@
         <v>7</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="I60" s="6" t="s">
         <v>67</v>
@@ -2863,7 +2899,7 @@
         <v>3000056</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="F61" s="1">
         <v>8</v>
@@ -2872,7 +2908,7 @@
         <v>7</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="I61" s="6" t="s">
         <v>67</v>
@@ -2889,7 +2925,7 @@
         <v>3000057</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F62" s="1">
         <v>1</v>
@@ -2898,7 +2934,7 @@
         <v>8</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="I62" s="6" t="s">
         <v>67</v>
@@ -2915,7 +2951,7 @@
         <v>3000058</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="F63" s="1">
         <v>2</v>
@@ -2924,7 +2960,7 @@
         <v>8</v>
       </c>
       <c r="H63" s="6" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="I63" s="6" t="s">
         <v>67</v>
@@ -2941,7 +2977,7 @@
         <v>3000059</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="F64" s="1">
         <v>3</v>
@@ -2950,7 +2986,7 @@
         <v>8</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="I64" s="6" t="s">
         <v>67</v>
@@ -2967,7 +3003,7 @@
         <v>3000060</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="F65" s="1">
         <v>4</v>
@@ -2976,7 +3012,7 @@
         <v>8</v>
       </c>
       <c r="H65" s="6" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="I65" s="6" t="s">
         <v>67</v>
@@ -2993,7 +3029,7 @@
         <v>3000061</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="F66" s="1">
         <v>5</v>
@@ -3002,7 +3038,7 @@
         <v>8</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="I66" s="6" t="s">
         <v>67</v>
@@ -3019,7 +3055,7 @@
         <v>3000062</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="F67" s="1">
         <v>6</v>
@@ -3028,7 +3064,7 @@
         <v>8</v>
       </c>
       <c r="H67" s="6" t="s">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="I67" s="6" t="s">
         <v>67</v>
@@ -3045,7 +3081,7 @@
         <v>3000063</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="F68" s="1">
         <v>7</v>
@@ -3054,7 +3090,7 @@
         <v>8</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="I68" s="6" t="s">
         <v>67</v>
@@ -3071,7 +3107,7 @@
         <v>3000064</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="F69" s="1">
         <v>8</v>
@@ -3080,7 +3116,7 @@
         <v>8</v>
       </c>
       <c r="H69" s="6" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="I69" s="6" t="s">
         <v>67</v>
@@ -3091,72 +3127,48 @@
     </row>
     <row r="70" customHeight="1" spans="4:10">
       <c r="D70" s="4"/>
-      <c r="E70" s="1"/>
-      <c r="F70" s="1"/>
-      <c r="G70" s="1"/>
       <c r="H70" s="1"/>
       <c r="I70" s="1"/>
       <c r="J70" s="1"/>
     </row>
     <row r="71" customHeight="1" spans="4:10">
       <c r="D71" s="4"/>
-      <c r="E71" s="1"/>
-      <c r="F71" s="1"/>
-      <c r="G71" s="1"/>
       <c r="H71" s="1"/>
       <c r="I71" s="1"/>
       <c r="J71" s="1"/>
     </row>
     <row r="72" customHeight="1" spans="4:10">
       <c r="D72" s="4"/>
-      <c r="E72" s="1"/>
-      <c r="F72" s="1"/>
-      <c r="G72" s="1"/>
       <c r="H72" s="1"/>
       <c r="I72" s="1"/>
       <c r="J72" s="1"/>
     </row>
     <row r="73" customHeight="1" spans="4:10">
       <c r="D73" s="4"/>
-      <c r="E73" s="1"/>
-      <c r="F73" s="1"/>
-      <c r="G73" s="1"/>
       <c r="H73" s="1"/>
       <c r="I73" s="1"/>
       <c r="J73" s="1"/>
     </row>
     <row r="74" customHeight="1" spans="4:10">
       <c r="D74" s="4"/>
-      <c r="E74" s="1"/>
-      <c r="F74" s="1"/>
-      <c r="G74" s="1"/>
       <c r="H74" s="1"/>
       <c r="I74" s="1"/>
       <c r="J74" s="1"/>
     </row>
     <row r="75" customHeight="1" spans="4:10">
       <c r="D75" s="4"/>
-      <c r="E75" s="1"/>
-      <c r="F75" s="1"/>
-      <c r="G75" s="1"/>
       <c r="H75" s="1"/>
       <c r="I75" s="1"/>
       <c r="J75" s="1"/>
     </row>
     <row r="76" customHeight="1" spans="4:10">
       <c r="D76" s="4"/>
-      <c r="E76" s="1"/>
-      <c r="F76" s="1"/>
-      <c r="G76" s="1"/>
       <c r="H76" s="1"/>
       <c r="I76" s="1"/>
       <c r="J76" s="1"/>
     </row>
     <row r="77" customHeight="1" spans="4:10">
       <c r="D77" s="4"/>
-      <c r="E77" s="1"/>
-      <c r="F77" s="1"/>
-      <c r="G77" s="1"/>
       <c r="H77" s="1"/>
       <c r="I77" s="1"/>
       <c r="J77" s="1"/>

--- a/Excel/FashionConfig.xlsx
+++ b/Excel/FashionConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27952" windowHeight="12255"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -81,7 +81,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="119">
   <si>
     <t>ID</t>
   </si>
@@ -369,6 +369,75 @@
   </si>
   <si>
     <t>魔神之靴</t>
+  </si>
+  <si>
+    <t>仙神之杖</t>
+  </si>
+  <si>
+    <t>7,33,2004,2007</t>
+  </si>
+  <si>
+    <t>仙神之衣</t>
+  </si>
+  <si>
+    <t>7,34,2005,2008</t>
+  </si>
+  <si>
+    <t>仙神之头</t>
+  </si>
+  <si>
+    <t>7,35,2006,2009</t>
+  </si>
+  <si>
+    <t>仙神之链</t>
+  </si>
+  <si>
+    <t>12,13,2001,2003</t>
+  </si>
+  <si>
+    <t>仙神之镯</t>
+  </si>
+  <si>
+    <t>仙神之戒</t>
+  </si>
+  <si>
+    <t>仙神之带</t>
+  </si>
+  <si>
+    <t>仙神之靴</t>
+  </si>
+  <si>
+    <t>邪神之杖</t>
+  </si>
+  <si>
+    <t>8,33,2004,2007</t>
+  </si>
+  <si>
+    <t>邪神之衣</t>
+  </si>
+  <si>
+    <t>8,34,2005,2008</t>
+  </si>
+  <si>
+    <t>邪神之头</t>
+  </si>
+  <si>
+    <t>8,35,2006,2009</t>
+  </si>
+  <si>
+    <t>邪神之链</t>
+  </si>
+  <si>
+    <t>邪神之镯</t>
+  </si>
+  <si>
+    <t>邪神之戒</t>
+  </si>
+  <si>
+    <t>邪神之带</t>
+  </si>
+  <si>
+    <t>邪神之靴</t>
   </si>
 </sst>
 </file>
@@ -1348,17 +1417,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J77"/>
+  <dimension ref="A1:J85"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="6.87610619469027" style="2" customWidth="1"/>
+    <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="9" style="2"/>
-    <col min="3" max="4" width="9.87610619469027" style="1" customWidth="1"/>
-    <col min="5" max="6" width="12.1238938053097" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12.5044247787611" style="1" customWidth="1"/>
-    <col min="8" max="8" width="17.7964601769912" style="2" customWidth="1"/>
-    <col min="9" max="9" width="10.1238938053097" style="2" customWidth="1"/>
-    <col min="10" max="10" width="14.8761061946903" style="2" customWidth="1"/>
+    <col min="3" max="4" width="9.875" style="1" customWidth="1"/>
+    <col min="5" max="6" width="12.125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.5083333333333" style="1" customWidth="1"/>
+    <col min="8" max="8" width="17.8" style="2" customWidth="1"/>
+    <col min="9" max="9" width="10.125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="14.875" style="2" customWidth="1"/>
     <col min="11" max="16371" width="9" style="2"/>
     <col min="16372" max="16384" width="9" style="1"/>
   </cols>
@@ -1461,7 +1530,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:10">
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -1487,7 +1556,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:10">
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="C7" s="1">
         <v>2</v>
       </c>
@@ -1513,7 +1582,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:10">
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="C8" s="1">
         <v>3</v>
       </c>
@@ -1539,7 +1608,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:10">
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="C9" s="1">
         <v>4</v>
       </c>
@@ -1565,7 +1634,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:10">
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="C10" s="1">
         <v>5</v>
       </c>
@@ -1591,7 +1660,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:10">
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="C11" s="1">
         <v>6</v>
       </c>
@@ -1617,7 +1686,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="3:10">
+    <row r="12" customHeight="1" spans="1:10">
       <c r="C12" s="1">
         <v>7</v>
       </c>
@@ -1643,7 +1712,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" customHeight="1" spans="3:10">
+    <row r="13" customHeight="1" spans="1:10">
       <c r="C13" s="1">
         <v>8</v>
       </c>
@@ -1669,7 +1738,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:10">
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="C14" s="1">
         <v>9</v>
       </c>
@@ -1695,7 +1764,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:10">
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="C15" s="1">
         <v>10</v>
       </c>
@@ -1721,7 +1790,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:10">
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="C16" s="1">
         <v>11</v>
       </c>
@@ -3125,53 +3194,421 @@
         <v>67</v>
       </c>
     </row>
-    <row r="70" customHeight="1" spans="4:10">
-      <c r="D70" s="4"/>
-      <c r="H70" s="1"/>
-      <c r="I70" s="1"/>
-      <c r="J70" s="1"/>
-    </row>
-    <row r="71" customHeight="1" spans="4:10">
-      <c r="D71" s="4"/>
-      <c r="H71" s="1"/>
-      <c r="I71" s="1"/>
-      <c r="J71" s="1"/>
-    </row>
-    <row r="72" customHeight="1" spans="4:10">
-      <c r="D72" s="4"/>
-      <c r="H72" s="1"/>
-      <c r="I72" s="1"/>
-      <c r="J72" s="1"/>
-    </row>
-    <row r="73" customHeight="1" spans="4:10">
-      <c r="D73" s="4"/>
-      <c r="H73" s="1"/>
-      <c r="I73" s="1"/>
-      <c r="J73" s="1"/>
-    </row>
-    <row r="74" customHeight="1" spans="4:10">
-      <c r="D74" s="4"/>
-      <c r="H74" s="1"/>
-      <c r="I74" s="1"/>
-      <c r="J74" s="1"/>
-    </row>
-    <row r="75" customHeight="1" spans="4:10">
-      <c r="D75" s="4"/>
-      <c r="H75" s="1"/>
-      <c r="I75" s="1"/>
-      <c r="J75" s="1"/>
-    </row>
-    <row r="76" customHeight="1" spans="4:10">
-      <c r="D76" s="4"/>
-      <c r="H76" s="1"/>
-      <c r="I76" s="1"/>
-      <c r="J76" s="1"/>
-    </row>
-    <row r="77" customHeight="1" spans="4:10">
-      <c r="D77" s="4"/>
-      <c r="H77" s="1"/>
-      <c r="I77" s="1"/>
-      <c r="J77" s="1"/>
+    <row r="70" customHeight="1" spans="3:10">
+      <c r="C70" s="1">
+        <v>65</v>
+      </c>
+      <c r="D70" s="4">
+        <v>3000065</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F70" s="1">
+        <v>1</v>
+      </c>
+      <c r="G70" s="1">
+        <v>9</v>
+      </c>
+      <c r="H70" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I70" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J70" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="71" customHeight="1" spans="3:10">
+      <c r="C71" s="1">
+        <v>66</v>
+      </c>
+      <c r="D71" s="4">
+        <v>3000066</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F71" s="1">
+        <v>2</v>
+      </c>
+      <c r="G71" s="1">
+        <v>9</v>
+      </c>
+      <c r="H71" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="I71" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J71" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="72" customHeight="1" spans="3:10">
+      <c r="C72" s="1">
+        <v>67</v>
+      </c>
+      <c r="D72" s="4">
+        <v>3000067</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F72" s="1">
+        <v>3</v>
+      </c>
+      <c r="G72" s="1">
+        <v>9</v>
+      </c>
+      <c r="H72" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="I72" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J72" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="73" customHeight="1" spans="3:10">
+      <c r="C73" s="1">
+        <v>68</v>
+      </c>
+      <c r="D73" s="4">
+        <v>3000068</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F73" s="1">
+        <v>4</v>
+      </c>
+      <c r="G73" s="1">
+        <v>9</v>
+      </c>
+      <c r="H73" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="I73" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J73" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="74" customHeight="1" spans="3:10">
+      <c r="C74" s="1">
+        <v>69</v>
+      </c>
+      <c r="D74" s="4">
+        <v>3000069</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="F74" s="1">
+        <v>5</v>
+      </c>
+      <c r="G74" s="1">
+        <v>9</v>
+      </c>
+      <c r="H74" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I74" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J74" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="75" customHeight="1" spans="3:10">
+      <c r="C75" s="1">
+        <v>70</v>
+      </c>
+      <c r="D75" s="4">
+        <v>3000070</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="F75" s="1">
+        <v>6</v>
+      </c>
+      <c r="G75" s="1">
+        <v>9</v>
+      </c>
+      <c r="H75" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="I75" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J75" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="76" customHeight="1" spans="3:10">
+      <c r="C76" s="1">
+        <v>71</v>
+      </c>
+      <c r="D76" s="4">
+        <v>3000071</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F76" s="1">
+        <v>7</v>
+      </c>
+      <c r="G76" s="1">
+        <v>9</v>
+      </c>
+      <c r="H76" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="I76" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J76" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="77" customHeight="1" spans="3:10">
+      <c r="C77" s="1">
+        <v>72</v>
+      </c>
+      <c r="D77" s="4">
+        <v>3000072</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F77" s="1">
+        <v>8</v>
+      </c>
+      <c r="G77" s="1">
+        <v>9</v>
+      </c>
+      <c r="H77" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="I77" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J77" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="78" customHeight="1" spans="3:10">
+      <c r="C78" s="1">
+        <v>73</v>
+      </c>
+      <c r="D78" s="4">
+        <v>3000073</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F78" s="1">
+        <v>1</v>
+      </c>
+      <c r="G78" s="1">
+        <v>10</v>
+      </c>
+      <c r="H78" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="I78" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J78" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="79" customHeight="1" spans="3:10">
+      <c r="C79" s="1">
+        <v>74</v>
+      </c>
+      <c r="D79" s="4">
+        <v>3000074</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F79" s="1">
+        <v>2</v>
+      </c>
+      <c r="G79" s="1">
+        <v>10</v>
+      </c>
+      <c r="H79" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="I79" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J79" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="80" customHeight="1" spans="3:10">
+      <c r="C80" s="1">
+        <v>75</v>
+      </c>
+      <c r="D80" s="4">
+        <v>3000075</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="F80" s="1">
+        <v>3</v>
+      </c>
+      <c r="G80" s="1">
+        <v>10</v>
+      </c>
+      <c r="H80" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="I80" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J80" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="81" customHeight="1" spans="3:10">
+      <c r="C81" s="1">
+        <v>76</v>
+      </c>
+      <c r="D81" s="4">
+        <v>3000076</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F81" s="1">
+        <v>4</v>
+      </c>
+      <c r="G81" s="1">
+        <v>10</v>
+      </c>
+      <c r="H81" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="I81" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J81" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="82" customHeight="1" spans="3:10">
+      <c r="C82" s="1">
+        <v>77</v>
+      </c>
+      <c r="D82" s="4">
+        <v>3000077</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F82" s="1">
+        <v>5</v>
+      </c>
+      <c r="G82" s="1">
+        <v>10</v>
+      </c>
+      <c r="H82" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="I82" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J82" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="83" customHeight="1" spans="3:10">
+      <c r="C83" s="1">
+        <v>78</v>
+      </c>
+      <c r="D83" s="4">
+        <v>3000078</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="F83" s="1">
+        <v>6</v>
+      </c>
+      <c r="G83" s="1">
+        <v>10</v>
+      </c>
+      <c r="H83" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="I83" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J83" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="84" customHeight="1" spans="3:10">
+      <c r="C84" s="1">
+        <v>79</v>
+      </c>
+      <c r="D84" s="4">
+        <v>3000079</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F84" s="1">
+        <v>7</v>
+      </c>
+      <c r="G84" s="1">
+        <v>10</v>
+      </c>
+      <c r="H84" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="I84" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J84" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="85" customHeight="1" spans="3:10">
+      <c r="C85" s="1">
+        <v>80</v>
+      </c>
+      <c r="D85" s="4">
+        <v>3000080</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F85" s="1">
+        <v>8</v>
+      </c>
+      <c r="G85" s="1">
+        <v>10</v>
+      </c>
+      <c r="H85" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="I85" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J85" s="6" t="s">
+        <v>67</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
